--- a/out/Attention-MambaAMT_repeat_4_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.623677129033441</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.780723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.2554444171274072</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.780723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.023677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.023677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.623677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.623677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.623677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.780723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.780723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.780723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.780723568071307</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000304407829681877</v>
+        <v>-0.0004499999204052146</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3917963785671953</v>
+        <v>0.5791847404061293</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7843346462320956</v>
+        <v>1.159465998829599</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09048198511666734</v>
+        <v>-0.133757660132265</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.023677129033441</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3010099856208458</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.780723568071307</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3010099856208458</v>
+        <v>0.4449770803534591</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.180723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3007504301649667</v>
+        <v>0.4443663517753698</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7974103320733427</v>
+        <v>1.876290111476057</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.623677129033441</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.897159249844379</v>
+        <v>4.200683032065338</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1525755441955396</v>
+        <v>0.3590069714438267</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.180723568071307</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.403736016826501</v>
+        <v>3.039668584609843</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2672503180949342</v>
+        <v>0.6288349755558031</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.785736335658729</v>
+        <v>3.938507422601589</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1463562378490482</v>
+        <v>0.3443729162937117</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.810967704187088</v>
+        <v>3.997876261879584</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06044706084826611</v>
+        <v>0.1422308328197048</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.78535255507279</v>
+        <v>3.937604395058679</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07531185059967514</v>
+        <v>0.1772074122656409</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.87553992929203</v>
+        <v>4.14981284767836</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04534805286343789</v>
+        <v>0.1067023430771687</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.890872096353753</v>
+        <v>4.18588888725746</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03447671101401142</v>
+        <v>0.08112156732495591</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.914458087740593</v>
+        <v>4.241385881078289</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01524902524526517</v>
+        <v>0.03588107473168791</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.910449133157324</v>
+        <v>4.231953117880448</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01209909449180475</v>
+        <v>0.02847190300085353</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.919393903366869</v>
+        <v>4.253002926737672</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005996051151668807</v>
+        <v>0.01411835756662029</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.919281778741284</v>
+        <v>4.252745859857683</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003486040894755449</v>
+        <v>0.008207673704912195</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.920252136963049</v>
+        <v>4.255035390074385</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001740520447377725</v>
+        <v>0.004099882252083282</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.92024496367226</v>
+        <v>4.25502527921888</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008573944487145107</v>
+        <v>0.002024501602641482</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.920218133023043</v>
+        <v>4.254968904424387</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004956479166854104</v>
+        <v>0.001173191430599666</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.920351580752899</v>
+        <v>4.255289718081982</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001623977585478931</v>
+        <v>0.0003878267400590558</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.920180318453953</v>
+        <v>4.254893448876043</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.809427244902859e-05</v>
+        <v>0.0001926296209598518</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.920176251748014</v>
+        <v>4.254890649528957</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>0.0001026326297247743</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.920178818035122</v>
+        <v>4.254903372102754</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>4.714396983319175e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.920172345230954</v>
+        <v>4.254894881847137</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>2.700120820192495e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.920172723799199</v>
+        <v>4.254902254365176</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>1.046497567870175e-05</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.920166056835328</v>
+        <v>4.254893249783534</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>3.872723086529542e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.920162194760232</v>
+        <v>4.254890521953073</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.920157647448047</v>
+        <v>4.254886202961924</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.920157737392697</v>
+        <v>4.254881378789035</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.920156879459112</v>
+        <v>4.25488052085545</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.920157107780147</v>
+        <v>4.254880749176484</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.920156312115935</v>
+        <v>4.254879953512273</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.920156374385308</v>
+        <v>4.254880015781645</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.920156402060585</v>
+        <v>4.254880043456923</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.920156554274608</v>
+        <v>4.254880195670945</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.920156208333646</v>
+        <v>4.254879849729984</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.920156284440658</v>
+        <v>4.254879925836995</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.92015645049232</v>
+        <v>4.254880091888657</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.920156810270919</v>
+        <v>4.254880451667257</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.920156831027377</v>
+        <v>4.254880472423714</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.920156934809666</v>
+        <v>4.254880576206003</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.920157163130701</v>
+        <v>4.254880804527038</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.920157038591954</v>
+        <v>4.254880679988292</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.920157066267231</v>
+        <v>4.254880707663569</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.920157121617785</v>
+        <v>4.254880763014123</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.920157384532916</v>
+        <v>4.254881025929254</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.920157301507085</v>
+        <v>4.254880942903423</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.920157093942508</v>
+        <v>4.254880735338846</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.920157107780147</v>
+        <v>4.254880749176484</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.920157246156531</v>
+        <v>4.254880887552869</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.920156962484943</v>
+        <v>4.254880603881281</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.920156789514462</v>
+        <v>4.254880430910799</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.920156685732174</v>
+        <v>4.254880327128511</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.920156831027377</v>
+        <v>4.254880472423714</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.920157073186051</v>
+        <v>4.254880714582388</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.92015690021557</v>
+        <v>4.254880541611907</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.920156602706343</v>
+        <v>4.25488024410268</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.920156588868704</v>
+        <v>4.254880230265042</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.920156222171285</v>
+        <v>4.254879863567623</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.920156222171285</v>
+        <v>4.254879863567623</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.920156159901912</v>
+        <v>4.25487980129825</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.920156056119623</v>
+        <v>4.25487969751596</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.920155883149142</v>
+        <v>4.254879524545481</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.920155931580877</v>
+        <v>4.254879572977215</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.920155571802277</v>
+        <v>4.254879213198614</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.920155530289362</v>
+        <v>4.254879171685699</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.920155585639916</v>
+        <v>4.254879227036254</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.92015564099047</v>
+        <v>4.254879282386807</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.920155682503385</v>
+        <v>4.254879323899723</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.920155412669435</v>
+        <v>4.254879054065772</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.920155468019988</v>
+        <v>4.254879109416327</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.920155613315192</v>
+        <v>4.25487925471153</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.920155578721096</v>
+        <v>4.254879220117434</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.920155564883458</v>
+        <v>4.254879206279796</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.920155654828108</v>
+        <v>4.254879296224445</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.920155973093792</v>
+        <v>4.25487961449013</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.920155793204492</v>
+        <v>4.25487943460083</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.920155834717408</v>
+        <v>4.254879476113746</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.920155647909289</v>
+        <v>4.254879289305626</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.920155717097481</v>
+        <v>4.254879358493818</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.920155516451723</v>
+        <v>4.254879157848061</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.920155557964639</v>
+        <v>4.254879199360976</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.8554444171274072</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.920155585639916</v>
+        <v>4.254879227036254</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.7476643170515025</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.7476643170515025</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.7476643170515025</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.7476643170515025</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.7476643170515025</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000304407829681877</v>
+        <v>-0.0002349178190187086</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3917963785671953</v>
+        <v>0.3023575322944033</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7843346462320956</v>
+        <v>0.6052872704823259</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09048198511666734</v>
+        <v>-0.06982678207805348</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.023677129033441</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3010099856208458</v>
+        <v>0.232295832397331</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3010099856208458</v>
+        <v>0.232295832397331</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3007504301649667</v>
+        <v>0.2321378811157951</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7974103320733427</v>
+        <v>0.4852603346262142</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.897159249844379</v>
+        <v>1.203625142297861</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1525755441955396</v>
+        <v>0.09284915938208864</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.403736016826501</v>
+        <v>0.9033546589326649</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2672503180949342</v>
+        <v>0.1626338907579483</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203253</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.785736335658729</v>
+        <v>1.135819230489844</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1463562378490482</v>
+        <v>0.08906423692321729</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.810967704187088</v>
+        <v>1.151173674504036</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06044706084826611</v>
+        <v>0.03678482691736559</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.78535255507279</v>
+        <v>1.135585641306296</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07531185059967514</v>
+        <v>0.04583073767787688</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.87553992929203</v>
+        <v>1.190469052012818</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04534805286343789</v>
+        <v>0.02759602414691862</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.890872096353753</v>
+        <v>1.199799462573742</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03447671101401142</v>
+        <v>0.02098129496070439</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.914458087740593</v>
+        <v>1.214153054539831</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01524902524526517</v>
+        <v>0.009278054954948305</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.910449133157324</v>
+        <v>1.211711390784792</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01209909449180475</v>
+        <v>0.007359858494700953</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.919393903366869</v>
+        <v>1.217152902864953</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005996051151668807</v>
+        <v>0.003647161184425369</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.180723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.919281778741284</v>
+        <v>1.217082700095604</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003486040894755449</v>
+        <v>0.002118716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.920252136963049</v>
+        <v>1.21767145122418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001740520447377725</v>
+        <v>0.001056858272154783</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.92024496367226</v>
+        <v>1.217665129138949</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008573944487145107</v>
+        <v>0.0005210606137158515</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.920218133023043</v>
+        <v>1.217646812442927</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004956479166854104</v>
+        <v>0.0002987264027891491</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.920351580752899</v>
+        <v>1.217726267626595</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001623977585478931</v>
+        <v>9.767062524270776e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.920180318453953</v>
+        <v>1.217619293416574</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.809427244902859e-05</v>
+        <v>4.665319638723399e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.920176251748014</v>
+        <v>1.217614864970567</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>2.190815743119357e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203253</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.920178818035122</v>
+        <v>1.217614446098334</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>9.221082681779568e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.920172345230954</v>
+        <v>1.217608514966896</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.920172723799199</v>
+        <v>1.217606742107844</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.920166056835328</v>
+        <v>1.217600742574247</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.920162194760232</v>
+        <v>1.217596499964093</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.920157647448047</v>
+        <v>1.217596728285128</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.920157737392697</v>
+        <v>1.217596818229778</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.920156879459112</v>
+        <v>1.217595960296193</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.920157107780147</v>
+        <v>1.217596188617228</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.920156312115935</v>
+        <v>1.217595392953016</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.920156374385308</v>
+        <v>1.217595455222389</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.920156402060585</v>
+        <v>1.217595482897666</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.780723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.920156554274608</v>
+        <v>1.217595635111689</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.023677129033441</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.920156208333646</v>
+        <v>1.217595289170727</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.780723568071307</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.920156284440658</v>
+        <v>1.217595365277739</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.92015645049232</v>
+        <v>1.2175955313294</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.920156810270919</v>
+        <v>1.217595891108</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.920156831027377</v>
+        <v>1.217595911864458</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.920156934809666</v>
+        <v>1.217596015646746</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.920157163130701</v>
+        <v>1.217596243967781</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.920157038591954</v>
+        <v>1.217596119429035</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.920157066267231</v>
+        <v>1.217596147104312</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.920157121617785</v>
+        <v>1.217596202454866</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.920157384532916</v>
+        <v>1.217596465369997</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.920157301507085</v>
+        <v>1.217596382344166</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203253</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.920157093942508</v>
+        <v>1.217596174779589</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.780723568071307</v>
+        <v>0.9753533038203253</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.920157107780147</v>
+        <v>1.217596188617228</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.920157246156531</v>
+        <v>1.217596326993612</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.920156962484943</v>
+        <v>1.217596043322023</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.180723568071307</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.920156789514462</v>
+        <v>1.217595870351543</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.180723568071307</v>
+        <v>0.9753533038203253</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.920156685732174</v>
+        <v>1.217595766569255</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.920156831027377</v>
+        <v>1.217595911864458</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.920157073186051</v>
+        <v>1.217596154023131</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.623677129033441</v>
+        <v>0.3343474301963825</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.92015690021557</v>
+        <v>1.217595981052651</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.920156602706343</v>
+        <v>1.217595683543424</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.920156588868704</v>
+        <v>1.217595669705785</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.920156222171285</v>
+        <v>1.217595303008365</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.920156222171285</v>
+        <v>1.217595303008365</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.920156159901912</v>
+        <v>1.217595240738993</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.920156056119623</v>
+        <v>1.217595136956704</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.920155883149142</v>
+        <v>1.217594963986223</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.920155931580877</v>
+        <v>1.217595012417958</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.920155571802277</v>
+        <v>1.217594652639358</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.180723568071307</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.920155530289362</v>
+        <v>1.217594611126442</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.920155585639916</v>
+        <v>1.217594666476996</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.92015564099047</v>
+        <v>1.21759472182755</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.920155682503385</v>
+        <v>1.217594763340466</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.920155412669435</v>
+        <v>1.217594493506515</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.920155468019988</v>
+        <v>1.217594548857069</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.780723568071307</v>
+        <v>1.175353303820325</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.920155613315192</v>
+        <v>1.217594694152273</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.920155578721096</v>
+        <v>1.217594659558177</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.023677129033441</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.920155564883458</v>
+        <v>1.217594645720539</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.920155654828108</v>
+        <v>1.217594735665189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.780723568071307</v>
+        <v>0.5343474301963825</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.920155973093792</v>
+        <v>1.217595053930873</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.023677129033441</v>
+        <v>-0.10665844342756</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.920155793204492</v>
+        <v>1.217594874041573</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.920155834717408</v>
+        <v>1.217594915554489</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.920155647909289</v>
+        <v>1.21759472874637</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.920155717097481</v>
+        <v>1.217594797934562</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.9476643170515026</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.920155516451723</v>
+        <v>1.217594597288804</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.623677129033441</v>
+        <v>-0.30665844342756</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.920155557964639</v>
+        <v>1.21759463880172</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.780723568071307</v>
+        <v>0.01384449338441125</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.920155585639916</v>
+        <v>1.217594666476996</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0143856406211853</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005578884854912758</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007993442937731743</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.007504042237997055</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01016018353402615</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.008792394772171974</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003923758864402771</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.007452268153429031</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.007769400253891945</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.008825439959764481</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.004284083843231201</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.10665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.00197446346282959</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.10665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.007536450400948524</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.10665844342756</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.003919638693332672</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7476643170515025</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0005719047039747238</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7476643170515025</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0005073137581348419</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.005588367581367493</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.008952802047133446</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.006840905174612999</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01052893698215485</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.01172798033803701</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001492792740464211</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.002359604462981224</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.008909257128834724</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.003812963142991066</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.005169762298464775</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01534361578524113</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.006788162514567375</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.009771829470992088</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7476643170515025</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01358003169298172</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7476643170515025</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01599086634814739</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.007176686078310013</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005651017650961876</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.009390706196427345</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.10665844342756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.01312292646616697</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.009857945144176483</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7476643170515025</v>
+        <v>0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003309100866317749</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.01143145840615034</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9476643170515026</v>
+        <v>0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0116286464035511</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.30665844342756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006558464840054512</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02477186359465122</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.05032435059547424</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.175353303820325</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.03939095884561539</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.175353303820325</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002349178190187086</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3023575322944033</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01080782152712345</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6052872704823259</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06982678207805348</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.02968772128224373</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.232295832397331</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.04084405303001404</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.232295832397331</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.04283760488033295</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2321378811157951</v>
+        <v>0.1805213941220674</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4852603346262142</v>
+        <v>0.271009254272278</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01320932991802692</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.203625142297861</v>
+        <v>0.7230795454343113</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.09284915938208864</v>
+        <v>0.05185450506984655</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.04906698316335678</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9033546589326649</v>
+        <v>0.5553839406986648</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1626338907579483</v>
+        <v>0.09082808341202726</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01724802143871784</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9753533038203253</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.135819230489844</v>
+        <v>0.6852113324793528</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.08906423692321729</v>
+        <v>0.0497410020264745</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01458418555557728</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.175353303820325</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.151173674504036</v>
+        <v>0.6937865293520289</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03678482691736559</v>
+        <v>0.02054356141809943</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.03060021810233593</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.135585641306296</v>
+        <v>0.6850809000840403</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04583073767787688</v>
+        <v>0.02559600501737523</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.03844430297613144</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.190469052012818</v>
+        <v>0.7157324032888799</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02759602414691862</v>
+        <v>0.01541210131699671</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.03712476789951324</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.199799462573742</v>
+        <v>0.7209432314776005</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02098129496070439</v>
+        <v>0.01171606775438062</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01958859898149967</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.214153054539831</v>
+        <v>0.7289579523447307</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.009278054954948305</v>
+        <v>0.005179270717863615</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.001296386122703552</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.211711390784792</v>
+        <v>0.7275921584448952</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.007359858494700953</v>
+        <v>0.004108727467416868</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.05097150057554245</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.175353303820325</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.217152902864953</v>
+        <v>0.7306288494663095</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003647161184425369</v>
+        <v>0.002033706414593613</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.05163734406232834</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.217082700095604</v>
+        <v>0.7305874428601901</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002118716544309565</v>
+        <v>0.001181953904216853</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03416895866394043</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.21767145122418</v>
+        <v>0.7309140646555904</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001056858272154783</v>
+        <v>0.0005884769521084263</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.008080413565039635</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.217665129138949</v>
+        <v>0.7309083257367219</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005210606137158515</v>
+        <v>0.0002882141125629336</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.03434792906045914</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.217646812442927</v>
+        <v>0.7308959033159879</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002987264027891491</v>
+        <v>0.0001652202916730396</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001624220982193947</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.217726267626595</v>
+        <v>0.7309379755441389</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>9.767062524270776e-05</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002832623198628426</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.217619293416574</v>
+        <v>0.7308764477667462</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>4.665319638723399e-05</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01482719369232655</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.217614864970567</v>
+        <v>0.7308717708190028</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.190815743119357e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001160278916358948</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9753533038203253</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.217614446098334</v>
+        <v>0.730869360818584</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.221082681779568e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.04046780616044998</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.217608514966896</v>
+        <v>0.7308638191458536</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.008261242881417274</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.217606742107844</v>
+        <v>0.7308609705731517</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.02536565251648426</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.217600742574247</v>
+        <v>0.7308553031428779</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.03652727603912354</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.175353303820325</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.217596499964093</v>
+        <v>0.7308556836779357</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0006092917174100876</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.217596728285128</v>
+        <v>0.7308559119989705</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01751292496919632</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.217596818229778</v>
+        <v>0.7308560019436204</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.003292696550488472</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.217595960296193</v>
+        <v>0.7308551440100356</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.009977109730243683</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.217596188617228</v>
+        <v>0.7308553723310702</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006488339975476265</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.217595392953016</v>
+        <v>0.7308545766668585</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01205451786518097</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.217595455222389</v>
+        <v>0.7308546389362316</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0110387671738863</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.217595482897666</v>
+        <v>0.7308546666115084</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01088572107255459</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.217595635111689</v>
+        <v>0.7308548188255317</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01059001125395298</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5343474301963825</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.217595289170727</v>
+        <v>0.7308544728845701</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01482031680643559</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.217595365277739</v>
+        <v>0.7308545489915816</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006351236253976822</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.2175955313294</v>
+        <v>0.7308547150432433</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.03112303651869297</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.217595891108</v>
+        <v>0.7308550748218433</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01657436601817608</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.217595911864458</v>
+        <v>0.730855095578301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02983124740421772</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.217596015646746</v>
+        <v>0.7308551993605895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00606858916580677</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.175353303820325</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.217596243967781</v>
+        <v>0.7308554276816241</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0074263084679842</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.175353303820325</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.217596119429035</v>
+        <v>0.7308553031428779</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01053560338914394</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.175353303820325</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.217596147104312</v>
+        <v>0.7308553308181549</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0308841560035944</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5343474301963825</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.217596202454866</v>
+        <v>0.7308553861687088</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.007832406088709831</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.217596465369997</v>
+        <v>0.7308556490838395</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.00521809421479702</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3343474301963825</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.217596382344166</v>
+        <v>0.7308555660580087</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01100463606417179</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9753533038203253</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.217596174779589</v>
+        <v>0.730855358493432</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01154451258480549</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9753533038203253</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.217596188617228</v>
+        <v>0.7308553723310702</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.004285052418708801</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5343474301963825</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.217596326993612</v>
+        <v>0.730855510707455</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.006839990615844727</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3343474301963825</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.217596043322023</v>
+        <v>0.7308552270358664</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.003675531595945358</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3343474301963825</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.217595870351543</v>
+        <v>0.7308550540653856</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02200760878622532</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9753533038203253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.217595766569255</v>
+        <v>0.7308549502830971</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01357889361679554</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.217595911864458</v>
+        <v>0.730855095578301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.009300613775849342</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.217596154023131</v>
+        <v>0.7308553377369742</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01292378269135952</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3343474301963825</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.217595981052651</v>
+        <v>0.7308551647664933</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.004586117342114449</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.217595683543424</v>
+        <v>0.7308548672572663</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02252684161067009</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.217595669705785</v>
+        <v>0.7308548534196277</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003046538680791855</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.217595303008365</v>
+        <v>0.7308544867222085</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01796965859830379</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.217595303008365</v>
+        <v>0.7308544867222085</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02711748704314232</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.217595240738993</v>
+        <v>0.7308544244528354</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01000382006168365</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.217595136956704</v>
+        <v>0.730854320670547</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.002995079383254051</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.217594963986223</v>
+        <v>0.7308541477000662</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02006260119378567</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.217595012417958</v>
+        <v>0.7308541961318008</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02338445372879505</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.217594652639358</v>
+        <v>0.7308538363532007</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.003901932388544083</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.217594611126442</v>
+        <v>0.7308537948402853</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003983225673437119</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.217594666476996</v>
+        <v>0.730853850190839</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0008153971284627914</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.21759472182755</v>
+        <v>0.730853905541393</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00532153993844986</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.217594763340466</v>
+        <v>0.7308539470543084</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01399708725512028</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.30665844342756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.217594493506515</v>
+        <v>0.7308536772203583</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.009038040414452553</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.217594548857069</v>
+        <v>0.7308537325709122</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0009470190852880478</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.175353303820325</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.217594694152273</v>
+        <v>0.7308538778661161</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.008630754426121712</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.217594659558177</v>
+        <v>0.7308538432720199</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.0007634758949279785</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.217594645720539</v>
+        <v>0.7308538294343814</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02552983351051807</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.217594735665189</v>
+        <v>0.7308539193790315</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0242204163223505</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5343474301963825</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.217595053930873</v>
+        <v>0.7308542376447161</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.03211131319403648</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.10665844342756</v>
+        <v>0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.217594874041573</v>
+        <v>0.730854057755416</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01661082729697227</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.217594915554489</v>
+        <v>0.7308540992683314</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.008059512823820114</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.21759472874637</v>
+        <v>0.7308539124602121</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.0126976165920496</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.217594797934562</v>
+        <v>0.7308539816484046</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01308542303740978</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9476643170515026</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.217594597288804</v>
+        <v>0.7308537810026468</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.001382315531373024</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.30665844342756</v>
+        <v>-0.01999999999999946</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.21759463880172</v>
+        <v>0.7308538225155622</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01052957214415073</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.01384449338441125</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.217594666476996</v>
+        <v>0.730853850190839</v>
       </c>
     </row>
   </sheetData>
